--- a/src/main/resources/python/MultifacetedModeling/DataOutput/MLR/threshold_analysis.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/DataOutput/MLR/threshold_analysis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="result0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="result0" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.86</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.86</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.76</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.76</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.36</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.36</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.36</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.36</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.36</t>
         </is>
       </c>
     </row>
